--- a/配置表格/L灵气源配置表.xlsx
+++ b/配置表格/L灵气源配置表.xlsx
@@ -14,6 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="spirit_config" sheetId="1" r:id="rId1"/>
+    <sheet name="本轮配置说明" sheetId="2" r:id="rIdConfig2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -129,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,8 +163,36 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,8 +211,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -206,12 +257,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -223,6 +290,28 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -501,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.5" style="1" customWidth="1"/>
@@ -589,11 +678,11 @@
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
+      <c r="B4" t="str" s="1">
+        <v>灵气源ID（不是场景ID）</v>
+      </c>
+      <c r="C4" t="str" s="1">
+        <v>灵气源名称</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>18</v>
@@ -618,169 +707,572 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="14">
-      <c r="B5" s="4">
+      <c r="A5"/>
+      <c r="B5" t="n" s="4">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="4">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
+      <c r="C5" t="str" s="4">
+        <v>洞府·1阶</v>
+      </c>
+      <c r="D5" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E5" t="n" s="4">
+        <v>144</v>
+      </c>
+      <c r="F5" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n" s="4">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14">
+      <c r="A6"/>
+      <c r="B6" t="n" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="str" s="4">
+        <v>洞府·2阶</v>
+      </c>
+      <c r="D6" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E6" t="n" s="4">
+        <v>1584</v>
+      </c>
+      <c r="F6" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n" s="4">
+        <v>66</v>
+      </c>
+      <c r="H6" t="n" s="4">
         <v>1</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I6" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="14">
+      <c r="A7"/>
+      <c r="B7" t="n" s="4">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="str" s="4">
+        <v>洞府·3阶</v>
+      </c>
+      <c r="D7" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E7" t="n" s="4">
+        <v>3024</v>
+      </c>
+      <c r="F7" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n" s="4">
+        <v>126</v>
+      </c>
+      <c r="H7" t="n" s="4">
         <v>1</v>
       </c>
-      <c r="J5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="14">
-      <c r="B6" s="4">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="4">
-        <v>40</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="I7" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="14">
+      <c r="A8"/>
+      <c r="B8" t="n" s="4">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="str" s="4">
+        <v>洞府·4阶</v>
+      </c>
+      <c r="D8" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E8" t="n" s="4">
+        <v>4464</v>
+      </c>
+      <c r="F8" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n" s="4">
+        <v>186</v>
+      </c>
+      <c r="H8" t="n" s="4">
         <v>1</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I8" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="14">
+      <c r="A9"/>
+      <c r="B9" t="n" s="4">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="str" s="4">
+        <v>洞府·5阶</v>
+      </c>
+      <c r="D9" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E9" t="n" s="4">
+        <v>5904</v>
+      </c>
+      <c r="F9" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n" s="4">
+        <v>246</v>
+      </c>
+      <c r="H9" t="n" s="4">
         <v>1</v>
       </c>
-      <c r="J6" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="14">
-      <c r="B7" s="4">
-        <v>1003</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="4">
-        <v>55</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="I9" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14">
+      <c r="A10"/>
+      <c r="B10" t="n" s="4">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="str" s="4">
+        <v>洞府·6阶</v>
+      </c>
+      <c r="D10" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E10" t="n" s="4">
+        <v>7344</v>
+      </c>
+      <c r="F10" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n" s="4">
+        <v>306</v>
+      </c>
+      <c r="H10" t="n" s="4">
         <v>1</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I10" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11" t="n" s="4">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="str" s="4">
+        <v>洞府·7阶</v>
+      </c>
+      <c r="D11" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E11" t="n" s="4">
+        <v>8784</v>
+      </c>
+      <c r="F11" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n" s="4">
+        <v>366</v>
+      </c>
+      <c r="H11" t="n" s="4">
         <v>1</v>
       </c>
-      <c r="J7" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="14">
-      <c r="B8" s="4">
+      <c r="I11" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12" t="n" s="4">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="str" s="4">
+        <v>洞府·8阶</v>
+      </c>
+      <c r="D12" t="str" s="4">
+        <v>个人</v>
+      </c>
+      <c r="E12" t="n" s="4">
+        <v>10224</v>
+      </c>
+      <c r="F12" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n" s="4">
+        <v>426</v>
+      </c>
+      <c r="H12" t="n" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13" t="n" s="4">
         <v>2001</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="4">
-        <v>500</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>20</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="C13" t="str" s="4">
+        <v>寒潭秘境</v>
+      </c>
+      <c r="D13" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E13" t="n" s="4">
+        <v>216</v>
+      </c>
+      <c r="F13" t="n" s="4">
+        <v>1728</v>
+      </c>
+      <c r="G13" t="n" s="4">
+        <v>36</v>
+      </c>
+      <c r="H13" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14" t="n" s="4">
+        <v>2002</v>
+      </c>
+      <c r="C14" t="str" s="4">
+        <v>灵脉秘境</v>
+      </c>
+      <c r="D14" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E14" t="n" s="4">
+        <v>2376</v>
+      </c>
+      <c r="F14" t="n" s="4">
+        <v>19008</v>
+      </c>
+      <c r="G14" t="n" s="4">
+        <v>396</v>
+      </c>
+      <c r="H14" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15" t="n" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C15" t="str" s="4">
+        <v>金丹临时灵气源</v>
+      </c>
+      <c r="D15" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E15" t="n" s="4">
+        <v>4536</v>
+      </c>
+      <c r="F15" t="n" s="4">
+        <v>36288</v>
+      </c>
+      <c r="G15" t="n" s="4">
+        <v>756</v>
+      </c>
+      <c r="H15" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16" t="n" s="4">
+        <v>2004</v>
+      </c>
+      <c r="C16" t="str" s="4">
+        <v>元婴临时灵气源</v>
+      </c>
+      <c r="D16" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E16" t="n" s="4">
+        <v>6696</v>
+      </c>
+      <c r="F16" t="n" s="4">
+        <v>53568</v>
+      </c>
+      <c r="G16" t="n" s="4">
+        <v>1116</v>
+      </c>
+      <c r="H16" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17" t="n" s="4">
+        <v>2005</v>
+      </c>
+      <c r="C17" t="str" s="4">
+        <v>化神临时灵气源</v>
+      </c>
+      <c r="D17" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E17" t="n" s="4">
+        <v>8856</v>
+      </c>
+      <c r="F17" t="n" s="4">
+        <v>70848</v>
+      </c>
+      <c r="G17" t="n" s="4">
+        <v>1476</v>
+      </c>
+      <c r="H17" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18" t="n" s="4">
+        <v>2006</v>
+      </c>
+      <c r="C18" t="str" s="4">
+        <v>炼虚临时灵气源</v>
+      </c>
+      <c r="D18" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E18" t="n" s="4">
+        <v>11016</v>
+      </c>
+      <c r="F18" t="n" s="4">
+        <v>88128</v>
+      </c>
+      <c r="G18" t="n" s="4">
+        <v>1836</v>
+      </c>
+      <c r="H18" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19" t="n" s="4">
+        <v>2007</v>
+      </c>
+      <c r="C19" t="str" s="4">
+        <v>合体临时灵气源</v>
+      </c>
+      <c r="D19" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E19" t="n" s="4">
+        <v>13176</v>
+      </c>
+      <c r="F19" t="n" s="4">
+        <v>105408</v>
+      </c>
+      <c r="G19" t="n" s="4">
+        <v>2196</v>
+      </c>
+      <c r="H19" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20" t="n" s="4">
+        <v>2008</v>
+      </c>
+      <c r="C20" t="str" s="4">
+        <v>大乘临时灵气源</v>
+      </c>
+      <c r="D20" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E20" t="n" s="4">
+        <v>15336</v>
+      </c>
+      <c r="F20" t="n" s="4">
+        <v>122688</v>
+      </c>
+      <c r="G20" t="n" s="4">
+        <v>2556</v>
+      </c>
+      <c r="H20" t="n" s="4">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21" t="n" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C21" t="str" s="4">
+        <v>宗门修炼室（后续设施预留）</v>
+      </c>
+      <c r="D21" t="str" s="4">
+        <v>共享</v>
+      </c>
+      <c r="E21" t="n" s="4">
+        <v>200</v>
+      </c>
+      <c r="F21" t="n" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n" s="4">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n" s="4">
         <v>5</v>
       </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="14">
-      <c r="B9" s="4">
-        <v>2002</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="4">
-        <v>800</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4">
-        <v>35</v>
-      </c>
-      <c r="H9" s="4">
-        <v>5</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="14">
-      <c r="B10" s="4">
-        <v>3001</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="4">
-        <v>200</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4">
-        <v>8</v>
-      </c>
-      <c r="H10" s="4">
-        <v>5</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1">
-        <v>100</v>
+      <c r="I21" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="64" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>项目</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="12" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>完整内容草案，待用户审核；数值可调；非上线验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="263" customHeight="1">
+      <x:c r="A3" s="12" t="str">
+        <x:v>本轮工作</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>保留原source_id身份，扩个人洞府1001–1008和共享临时源2001–2008，3001宗门修炼室只作后续设施预留，共17条。source_id不是场景ID，表头中文应改作灵气源ID；源表不反向写场景，调用方用spirit_source_id单向引用。个人名额固定1，共享3名额，后到者只有基础打坐收益，不加入排队或双倍收益。
+个人每时辰产出取对应境界一层spirit_absorb×60%，上限=24时辰产出，spirit_total=0表示无限生命周期总量。共享产出=本境一层吸收×3人×120%，储量6时辰产出，实例总产量48时辰产出；产满后枯竭。全部额外转化/转化增幅先为0，避免高源速率又叠无依据转化倍率。所有速率按游戏时辰，不按真实小时；每刻结算1/8。
+洞府/临时实例缺spirit_source_id挂接与地图位置，需程序补入口、时限、名额、当前库存、累计产量存档与前台提醒，离线回个人洞府结算。3001不表示本期宗门设施租用已开放；本期宗门只上交购买。这些参数是以实际吸收属性为锚的可调预算，不承诺当前灵气修为增长已通过在线验证。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="12" t="str">
+        <x:v>交付边界</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>源文件未改；坐标/资源/程序挂接按需求清单另验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="12" t="str">
+        <x:v>详细说明</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>世界11_灵气源八境参数及预算.md</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>